--- a/data_extactor/batch_10_fa/batch_0043_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0043_fa.xlsx
@@ -493,42 +493,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Physician Assistants (دستیاران پزشک)</t>
+          <t>دستیاران پزشک (Physician Assistants)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cardiology Physician Assistant | Certified Physician Assistant (PA-C) | Emergency Medicine Physician Assistant (Emergency Medicine PA) | Family Practice Physician Assistant | Orthopaedic Physician Assistant | Orthopedic Physician Assistant | Physician Assistant (PA) | Physician's Assistant | Surgical Critical Care Physician Assistant (Surgical Critical Care PA) | Surgical Physician Assistant (Surgical PA)</t>
+          <t>دستیار پزشک در بخش قلب | دستیار پزشک دارای گواهی صلاحیت (PA-C) | دستیار پزشک طب اورژانس (Emergency Medicine PA) | دستیار پزشک طب خانواده | دستیار پزشک ارتوپدی | دستیار پزشک ارتوپدی | دستیار پزشک (PA) | دستیار پزشک | دستیار پزشک مراقبت‌های ویژه جراحی (Surgical Critical Care PA) | دستیار پزشک جراحی (Surgical PA)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ChartWare EMR | نرم‌افزار پرونده الکترونیک سلامت EMR | Epic Systems | سیستم کدگذاری رویه‌های رایج مراقبت‌های بهداشتی HCPCS | MEDITECH software | نرم‌افزار کدگذاری وضعیت پزشکی | نرم‌افزار کدگذاری رویه‌های پزشکی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word | نرم‌افزار مدیریت بیمار | نرم‌افزار سوابق بیمار برای دستیارهای دیجیتال شخصی PDAs | نرم‌افزار کنفرانس از راه دور | سیستم‌های تله‌رادیولوژی | نرم‌افزار مرورگر وب | نرم‌افزار eClinicalWorks EHR</t>
+          <t>ChartWare EMR | نرم‌افزار پرونده الکترونیک سلامت EMR | Epic Systems | سیستم کدگذاری رویه‌های رایج مراقبت‌های بهداشتی HCPCS | نرم‌افزار MEDITECH | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری رویه‌های پزشکی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word | نرم‌افزار مدیریت بیمار | نرم‌افزار سوابق بیمار برای دستیارهای دیجیتال شخصی PDAs | نرم‌افزار کنفرانس از راه دور | سیستم‌های تله‌رادیولوژی | نرم‌افزار مرورگر وب | نرم‌افزار eClinicalWorks EHR</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | سخنوری | نوشتار | گوش دادن فعال | یادگیری فعال | نظارت | علوم | راهبردهای یادگیری | ریاضیات</t>
+          <t>تفکر انتقادی | درک مطلب | سخن گفتن | نگارش | گوش دادن فعال | یادگیری فعال | نظارت | علوم | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | زبان انگلیسی | روان‌شناسی | درمان و مشاوره | خدمات مشتری و شخصی | آموزش و پرورش | جامعه‌شناسی و مردم‌شناسی | رایانه و الکترونیک | شیمی | ریاضیات | ایمنی و امنیت عمومی</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | زبان انگلیسی | روان‌شناسی | درمان و مشاوره | خدمات مشتری و شخصی | آموزش و پرورش | جامعه‌شناسی و انسان‌شناسی | رایانه و الکترونیک | شیمی | ریاضیات | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شنیداری | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک نوشتاری | بیان شفاهی | بیان نوشتاری | نظم‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | دید نزدیک | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | ثبات دست و بازو | سرعت ادراکی | استدلال ریاضی | تشخیص رنگ بصری | دید دور | مهارت انگشتان | روانی ایده‌ها</t>
+          <t>درک شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک کتبی | بیان شفاهی | بیان کتبی | ترتیب‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | ثبات دست و بازو | سرعت ادراکی | استدلال ریاضی | تشخیص رنگ بصری | بینایی دور | مهارت انگشتان | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>بحث‌های حضوری با افراد و درون تیم‌ها | ایمیل | تماس با دیگران | اهمیت دقیق یا صحیح بودن | مکالمات تلفنی | آزادی در تصمیم‌گیری | در معرض بیماری یا عفونت | تأثیر تصمیمات بر همکاران یا نتایج شرکت | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل محیطی | تناوب تصمیم‌گیری | نزدیکی فیزیکی | پیامد خطا | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | تعامل با مشتریان خارجی یا عموم مردم | سطح رقابت | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | نامه‌ها و یادداشت‌های کتبی | سلامت و ایمنی سایر کارکنان | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | موقعیت‌های تعارض‌آمیز</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ایمیل | ارتباط با دیگران | اهمیت دقیق یا درست بودن | مکالمات تلفنی | آزادی در تصمیم‌گیری | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | فراوانی تصمیم‌گیری | نزدیکی فیزیکی | پیامد خطا | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | تعامل با مشتریان خارجی یا عموم مردم | سطح رقابت | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نامه‌ها و یادداشت‌های کتبی | سلامت و ایمنی سایر کارکنان | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | موقعیت‌های تعارض</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Acute Care Nurses | Advanced Practice Psychiatric Nurses | Anesthesiologist Assistants | Anesthesiologists | Cardiologists | Clinical Nurse Specialists | Emergency Medicine Physicians | Family Medicine Physicians | General Internal Medicine Physicians | Medical Assistants | Neurologists | Nurse Practitioners | Obstetricians and Gynecologists | Orthopedic Surgeons, Except Pediatric | Paramedics | Pediatric Surgeons | Pediatricians, General | Physical Medicine and Rehabilitation Physicians | Registered Nurses | Urologists</t>
+          <t>پرستاران مراقبت‌های ویژه | پرستاران پیشرفته روانپزشکی | دستیاران متخصص بیهوشی | متخصصان بیهوشی | متخصصان قلب | متخصصان پرستاری بالینی | پزشکان طب اورژانس | پزشکان خانواده | پزشکان داخلی عمومی | دستیاران پزشکی | متخصصان مغز و اعصاب | پرستاران متخصص | متخصصان زنان و زایمان | جراحان ارتوپد، به‌جز کودکان | پارامدیک‌ها | جراحان کودکان | متخصصان کودکان، عمومی | پزشکان طب فیزیکی و توانبخشی | پرستاران ثبت‌شده | اورولوژیست‌ها</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -550,12 +550,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Anesthesiologist Assistants (دستیاران متخصص بیهوشی)</t>
+          <t>دستیاران متخصص بیهوشی (Anesthesiologist Assistants)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Anesthesia Assistant | Anesthesia Technician | Anesthesiologist Assistant | Anesthesiologists' Assistant | Cardiothoracic Anesthesia Technician | Certified Anesthesia Technician | Certified Anesthesiologist Assistant</t>
+          <t>دستیار بیهوشی | تکنسین بیهوشی | دستیار متخصص بیهوشی | دستیار متخصصان بیهوشی | تکنسین بیهوشی قلب و قفسه سینه | تکنسین بیهوشی دارای گواهی صلاحیت | دستیار متخصص بیهوشی دارای گواهی صلاحیت</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -565,27 +565,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | درک مطلب | نظارت | سخنوری | تفکر انتقادی | یادگیری فعال | نوشتار | علوم</t>
+          <t>گوش دادن فعال | درک مطلب | نظارت | سخن گفتن | تفکر انتقادی | یادگیری فعال | نگارش | علوم</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زبان انگلیسی | شیمی | خدمات مشتری و شخصی | ریاضیات | زیست‌شناسی | آموزش و پرورش | رایانه و الکترونیک</t>
+          <t>پزشکی و دندان‌پزشکی | زبان انگلیسی | شیمی | خدمات مشتری و شخصی | ریاضیات | زیست‌شناسی | آموزش و پرورش | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شنیداری | حساسیت به مسئله | درک نوشتاری | استدلال قیاسی | استدلال استقرایی | دید نزدیک | بیان شفاهی | سرعت ادراکی | توجه انتخابی | بیان نوشتاری | ثبات دست و بازو | نظم‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | دقت کنترل | انعطاف‌پذیری بستار | مهارت دستی | مهارت انگشتان | انعطاف‌پذیری دسته‌بندی | سرعت بستار | استدلال ریاضی | تشخیص رنگ بصری | اشتراک زمانی</t>
+          <t>درک شفاهی | حساسیت به مسئله | درک کتبی | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | بیان شفاهی | سرعت ادراکی | توجه انتخابی | بیان کتبی | ثبات دست و بازو | ترتیب‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | دقت کنترل | انعطاف‌پذیری بستار | مهارت دستی | مهارت انگشتان | انعطاف‌پذیری دسته‌بندی | سرعت بستار | استدلال ریاضی | تشخیص رنگ بصری | تقسیم توجه</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>در معرض بیماری یا عفونت | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | اهمیت دقیق یا صحیح بودن | محیط داخلی، دارای کنترل محیطی | بحث‌های حضوری با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | نزدیکی فیزیکی | تعیین وظایف، اولویت‌ها و اهداف | مکالمات تلفنی | سلامت و ایمنی سایر کارکنان | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | تماس با دیگران | آزادی در تصمیم‌گیری | پوشیدن تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، مهار ایمنی، لباس‌های محافظ کامل یا محافظ تابش | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای استفاده از دست‌ها جهت کار با، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | نتایج کاری و عملکرد سایر کارکنان | صرف زمان برای ایستادن | اهمیت تکرار وظایف یکسان | در معرض تابش | پیامد خطا | در معرض آلاینده‌ها | فشار زمانی | تناوب تصمیم‌گیری | صرف زمان برای راه رفتن یا دویدن | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | اهمیت دقیق یا درست بودن | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | نزدیکی فیزیکی | تعیین وظایف، اولویت‌ها و اهداف | مکالمات تلفنی | سلامت و ایمنی سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | ارتباط با دیگران | آزادی در تصمیم‌گیری | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | پیامدهای کاری و نتایج سایر کارکنان | صرف زمان برای ایستادن | اهمیت تکرار وظایف یکسان | قرار گرفتن در معرض تابش | پیامد خطا | قرار گرفتن در معرض آلاینده‌ها | فشار زمانی | فراوانی تصمیم‌گیری | صرف زمان برای راه رفتن یا دویدن | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Acute Care Nurses | Anesthesiologists | Cardiologists | Cardiovascular Technologists and Technicians | Clinical Nurse Specialists | Critical Care Nurses | Emergency Medical Technicians | Emergency Medicine Physicians | Nurse Anesthetists | Nurse Practitioners | Orthopedic Surgeons, Except Pediatric | Paramedics | Pediatric Surgeons | Physical Medicine and Rehabilitation Physicians | Physician Assistants | Radiation Therapists | Registered Nurses | Respiratory Therapists | Surgical Assistants | Surgical Technologists</t>
+          <t>پرستاران مراقبت‌های ویژه | متخصصان بیهوشی | متخصصان قلب | تکنولوژیست‌ها و تکنیسین‌های قلبی-عروقی | متخصصان پرستاری بالینی | پرستاران بخش مراقبت‌های ویژه | تکنسین‌های فوریت‌های پزشکی | پزشکان طب اورژانس | پرستاران بیهوشی | پرستاران متخصص | جراحان ارتوپد، به‌جز کودکان | پارامدیک‌ها | جراحان کودکان | پزشکان طب فیزیکی و توانبخشی | دستیاران پزشک | پرتودرمانگران | پرستاران ثبت‌شده | درمانگران تنفسی | دستیاران جراحی | تکنولوژیست‌های جراحی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -607,12 +607,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Podiatrists (پزشکان پا)</t>
+          <t>پزشکان پا (Podiatrists)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Attending Physician | Doctor Podiatric Medicine (DPM) | Doctor of Podiatric Medicine (DPM) | Doctor of Podiatric Medicine and Surgery (DPM and Surgery) | Foot and Ankle Surgeon | Physician | Podiatric Physician | Podiatric Surgeon | Podiatrist</t>
+          <t>پزشک معالج ارشد | دکترای طب پا (DPM) | دکترای طب پا (DPM) | دکترای طب و جراحی پا (DPM and Surgery) | جراح پا و مچ پا | پزشک | پزشک طب پا | جراح پا | متخصص طب پا</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -622,27 +622,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>یادگیری فعال | تفکر انتقادی | سخنوری | گوش دادن فعال | درک مطلب | نوشتار | نظارت | علوم | راهبردهای یادگیری</t>
+          <t>یادگیری فعال | تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | نظارت | علوم | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | خدمات مشتری و شخصی | زبان انگلیسی | آموزش و پرورش | رایانه و الکترونیک | زیست‌شناسی | مدیریت و اداره | روان‌شناسی | شیمی | پرسنل و منابع انسانی | اقتصاد و حسابداری | درمان و مشاوره | اداری</t>
+          <t>پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | زبان انگلیسی | آموزش و پرورش | رایانه و الکترونیک | زیست‌شناسی | مدیریت و اداره | روان‌شناسی | شیمی | پرسنل و منابع انسانی | اقتصاد و حسابداری | درمان و مشاوره | اداری</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | استدلال استقرایی | درک نوشتاری | بیان نوشتاری | حساسیت به مسئله | درک شنیداری | بیان شفاهی | تشخیص گفتار | وضوح گفتار | دید نزدیک | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | نظم‌دهی اطلاعات | روانی ایده‌ها | تجسم | سرعت بستار | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | توجه انتخابی | سرعت ادراکی | حافظه‌سپاری | اصالت</t>
+          <t>استدلال قیاسی | استدلال استقرایی | درک کتبی | بیان کتبی | حساسیت به مسئله | درک شفاهی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | روانی ایده‌ها | تجسم | سرعت بستار | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | توجه انتخابی | سرعت ادراکی | حفظ کردن | اصالت</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>آزادی در تصمیم‌گیری | بحث‌های حضوری با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | تماس با دیگران | اهمیت دقیق یا صحیح بودن | تناوب تصمیم‌گیری | در معرض بیماری یا عفونت | تأثیر تصمیمات بر همکاران یا نتایج شرکت | ایمیل | مکالمات تلفنی | نزدیکی فیزیکی | نتایج کاری و عملکرد سایر کارکنان | نامه‌ها و یادداشت‌های کتبی | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | سلامت و ایمنی سایر کارکنان | صرف زمان برای استفاده از دست‌ها جهت کار با، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | سطح رقابت | تعامل با مشتریان خارجی یا عموم مردم | محیط داخلی، دارای کنترل محیطی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | پیامد خطا | موقعیت‌های تعارض‌آمیز</t>
+          <t>آزادی در تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | اهمیت دقیق یا درست بودن | فراوانی تصمیم‌گیری | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | ایمیل | مکالمات تلفنی | نزدیکی فیزیکی | پیامدهای کاری و نتایج سایر کارکنان | نامه‌ها و یادداشت‌های کتبی | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | سلامت و ایمنی سایر کارکنان | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سطح رقابت | تعامل با مشتریان خارجی یا عموم مردم | محیط داخلی، دارای کنترل شرایط محیطی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | پیامد خطا | موقعیت‌های تعارض</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Allergists and Immunologists | Anesthesiologists | Cardiologists | Chiropractors | Dentists, General | Dermatologists | Emergency Medicine Physicians | General Internal Medicine Physicians | Medical Assistants | Naturopathic Physicians | Neurologists | Obstetricians and Gynecologists | Ophthalmologists, Except Pediatric | Optometrists | Oral and Maxillofacial Surgeons | Orthodontists | Orthopedic Surgeons, Except Pediatric | Pediatric Surgeons | Physical Medicine and Rehabilitation Physicians | Urologists</t>
+          <t>متخصصان آلرژی و ایمونولوژی | متخصصان بیهوشی | متخصصان قلب | کایروپراکتورها | دندانپزشکان، عمومی | متخصصان پوست | پزشکان طب اورژانس | پزشکان داخلی عمومی | دستیاران پزشکی | پزشکان ناتوروپاتی | متخصصان مغز و اعصاب | متخصصان زنان و زایمان | چشم‌پزشکان، به‌جز کودکان | اپتومتریست‌ها | جراحان دهان و فک و صورت | متخصصان ارتودنسی | جراحان ارتوپد، به‌جز کودکان | جراحان کودکان | پزشکان طب فیزیکی و توانبخشی | اورولوژیست‌ها</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -664,12 +664,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Occupational Therapists (کاردرمانگران)</t>
+          <t>کاردرمانگران (Occupational Therapists)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Assistive Technology Trainer | Certified Hand Therapist (CHT) | Early Intervention Occupational Therapist | Home Health Occupational Therapist | Industrial Rehabilitation Consultant | Occupational Therapist (OT) | Pediatric Occupational Therapist (Pediatric OT) | Pediatrics and Acute Care Occupational Therapist | Registered Occupational Therapist (OTR)</t>
+          <t>مربی فناوری‌های کمکی | کاردرمانگر دست دارای گواهی صلاحیت (CHT) | کاردرمانگر مداخله زودهنگام | کاردرمانگر بهداشت در منزل | مشاور توان‌بخشی صنعتی | کاردرمانگر (OT) | کاردرمانگر کودکان (Pediatric OT) | کاردرمانگر کودکان و مراقبت حاد | کاردرمانگر ثبت‌شده (OTR)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -679,27 +679,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | نظارت | تفکر انتقادی | سخنوری | نوشتار | درک مطلب | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | نظارت | تفکر انتقادی | سخن گفتن | نگارش | درک مطلب | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>درمان و مشاوره | روان‌شناسی | خدمات مشتری و شخصی | پزشکی و دندانپزشکی | زبان انگلیسی | آموزش و پرورش | زیست‌شناسی | جامعه‌شناسی و مردم‌شناسی</t>
+          <t>درمان و مشاوره | روان‌شناسی | خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | زبان انگلیسی | آموزش و پرورش | زیست‌شناسی | جامعه‌شناسی و انسان‌شناسی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>بیان شفاهی | بیان نوشتاری | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک شنیداری | درک نوشتاری | نظم‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | روانی ایده‌ها | اصالت | دید نزدیک | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | دید دور | مهارت انگشتان</t>
+          <t>بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | ترتیب‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | روانی ایده‌ها | اصالت | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | بینایی دور | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>بحث‌های حضوری با افراد و درون تیم‌ها | تماس با دیگران | ایمیل | محیط داخلی، دارای کنترل محیطی | تعیین وظایف، اولویت‌ها و اهداف | نزدیکی فیزیکی | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | تناوب تصمیم‌گیری | مکالمات تلفنی | در معرض بیماری یا عفونت | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فشار زمانی | سلامت و ایمنی سایر کارکنان | نامه‌ها و یادداشت‌های کتبی | صرف زمان برای استفاده از دست‌ها جهت کار با، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | تعامل با مشتریان خارجی یا عموم مردم | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | اهمیت دقیق یا صحیح بودن</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | تعیین وظایف، اولویت‌ها و اهداف | نزدیکی فیزیکی | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | فراوانی تصمیم‌گیری | مکالمات تلفنی | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فشار زمانی | سلامت و ایمنی سایر کارکنان | نامه‌ها و یادداشت‌های کتبی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | تعامل با مشتریان خارجی یا عموم مردم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | اهمیت دقیق یا درست بودن</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Acute Care Nurses | Advanced Practice Psychiatric Nurses | Clinical Nurse Specialists | Family Medicine Physicians | Low Vision Therapists, Orientation and Mobility Specialists, and Vision Rehabilitation Therapists | Mental Health Counselors | Mental Health and Substance Abuse Social Workers | Nurse Practitioners | Occupational Therapy Aides | Occupational Therapy Assistants | Physical Medicine and Rehabilitation Physicians | Physical Therapist Aides | Physical Therapist Assistants | Physical Therapists | Psychiatric Technicians | Psychiatrists | Recreational Therapists | Registered Nurses | Rehabilitation Counselors | Respiratory Therapists</t>
+          <t>پرستاران مراقبت‌های ویژه | پرستاران پیشرفته روانپزشکی | متخصصان پرستاری بالینی | پزشکان خانواده | درمانگران کم‌بینایی، متخصصان جهت‌یابی و تحرک، و درمانگران توانبخشی بینایی | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | پرستاران متخصص | کمک‌یاران کاردرمانی | دستیاران کاردرمانی | پزشکان طب فیزیکی و توانبخشی | کمک‌یاران فیزیوتراپی | دستیاران فیزیوتراپی | فیزیوتراپیست‌ها | تکنسین‌های روانپزشکی | روان‌پزشکان | درمانگران تفریحی | پرستاران ثبت‌شده | مشاوران توانبخشی | درمانگران تنفسی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -721,12 +721,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Low Vision Therapists, Orientation and Mobility Specialists, and Vision Rehabilitation Therapists (درمانگران کم‌بینایی، متخصصان جهت‌یابی و تحرک، و درمانگران توانبخشی بینایی)</t>
+          <t>درمانگران کم‌بینایی، متخصصان جهت‌یابی و تحرک، و درمانگران توانبخشی بینایی (Low Vision Therapists, Orientation and Mobility Specialists, and Vision Rehabilitation Therapists)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Certified Low Vision Therapist (CLVT) | Certified Orientation and Mobility Specialist (COMS) | Mobility Specialist | Orientation and Mobility Instructor (O and M Instructor) | Orientation and Mobility Specialist (O and M Specialist) | Rehabilitation Teacher | Rehabilitation Therapist | Students with Visual Impairments Teacher (TVI) | Vision Rehabilitation Therapist (VRT) | Visually Impaired Teacher (TVI)</t>
+          <t>درمانگر کم‌بینایی دارای گواهی صلاحیت (CLVT) | کارشناس جهت‌یابی و تحرک دارای گواهی صلاحیت (COMS) | کارشناس تحرک | مربی جهت‌یابی و تحرک (O and M) | کارشناس جهت‌یابی و تحرک (O and M) | مربی توان‌بخشی | درمانگر توانبخشی | معلم دانش‌آموزان دارای آسیب بینایی (TVI) | درمانگر توان‌بخشی بینایی (VRT) | معلم دانش‌آموزان دارای آسیب بینایی (TVI)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -736,27 +736,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>راهبردهای یادگیری | سخنوری | گوش دادن فعال | درک مطلب | نوشتار | یادگیری فعال | نظارت | تفکر انتقادی</t>
+          <t>راهبردهای یادگیری | سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | یادگیری فعال | نظارت | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | آموزش و پرورش | روان‌شناسی | حمل و نقل | خدمات مشتری و شخصی | درمان و مشاوره | ایمنی و امنیت عمومی | جامعه‌شناسی و مردم‌شناسی</t>
+          <t>زبان انگلیسی | آموزش و پرورش | روان‌شناسی | حمل و نقل | خدمات مشتری و شخصی | درمان و مشاوره | ایمنی و امنیت عمومی | جامعه‌شناسی و انسان‌شناسی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شنیداری | درک نوشتاری | حساسیت به مسئله | بیان نوشتاری | وضوح گفتار | تشخیص گفتار | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | نظم‌دهی اطلاعات | استدلال استقرایی | روانی ایده‌ها | اصالت | دید دور | دید نزدیک | توجه انتخابی</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | حساسیت به مسئله | بیان کتبی | وضوح گفتار | تشخیص گفتار | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال استقرایی | روانی ایده‌ها | اصالت | بینایی دور | بینایی نزدیک | توجه انتخابی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ایمیل | آزادی در تصمیم‌گیری | بحث‌های حضوری با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | نزدیکی فیزیکی | تماس با دیگران | مکالمات تلفنی | در وسیله نقلیه محصور یا کار با تجهیزات محصور | فضای باز، در معرض تمام شرایط آب و هوایی | کار با یا مشارکت در یک گروه کاری یا تیم | تعامل با مشتریان خارجی یا عموم مردم | تناوب تصمیم‌گیری | صرف زمان برای ایستادن | صرف زمان برای راه رفتن یا دویدن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | محیط داخلی، دارای کنترل محیطی</t>
+          <t>ایمیل | آزادی در تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | نزدیکی فیزیکی | ارتباط با دیگران | مکالمات تلفنی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | فضای باز، در معرض تمام شرایط آب و هوایی | کار با یا مشارکت در یک گروه کاری یا تیم | تعامل با مشتریان خارجی یا عموم مردم | فراوانی تصمیم‌گیری | صرف زمان برای ایستادن | صرف زمان برای راه رفتن یا دویدن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | محیط داخلی، دارای کنترل شرایط محیطی</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Adapted Physical Education Specialists | Marriage and Family Therapists | Mental Health Counselors | Mental Health and Substance Abuse Social Workers | Occupational Therapists | Occupational Therapy Aides | Occupational Therapy Assistants | Physical Medicine and Rehabilitation Physicians | Physical Therapist Aides | Physical Therapist Assistants | Physical Therapists | Psychiatric Aides | Psychiatric Technicians | Recreational Therapists | Rehabilitation Counselors | Special Education Teachers, Kindergarten | Special Education Teachers, Preschool | Special Education Teachers, Secondary School | Speech-Language Pathologists | Speech-Language Pathology Assistants</t>
+          <t>متخصصان تربیت بدنی تطبیقی | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | کاردرمانگران | کمک‌یاران کاردرمانی | دستیاران کاردرمانی | پزشکان طب فیزیکی و توانبخشی | کمک‌یاران فیزیوتراپی | دستیاران فیزیوتراپی | فیزیوتراپیست‌ها | کمک‌یاران روان‌پزشکی | تکنسین‌های روانپزشکی | درمانگران تفریحی | مشاوران توانبخشی | معلمان آموزش ویژه، کودکستان | معلمان آموزش ویژه، پیش‌دبستانی | معلمان آموزش ویژه، متوسطه | آسیب‌شناسان گفتار و زبان | دستیاران آسیب‌شناسی گفتار-زبان</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -778,42 +778,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Physical Therapists (فیزیوتراپیست‌ها)</t>
+          <t>فیزیوتراپیست‌ها (Physical Therapists)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Acute Care PT (Acute Care Physical Therapist) | Doctor of Physical Therapy (DPT) | Home Care Physical Therapist (Home Care PT) | Inpatient Physical Therapist (Inpatient PT) | Outpatient Physical Therapist (Outpatient PT) | Pediatric Physical Therapist (Pediatric PT) | Registered Physical Therapist (RPT) | Therapist</t>
+          <t>PT مراقبت حاد (فیزیوتراپیست مراقبت حاد) | دکترای فیزیوتراپی (DPT) | فیزیوتراپیست مراقبت در منزل (Home Care PT) | فیزیوتراپیست بستری (Inpatient PT) | فیزیوتراپیست سرپایی (Outpatient PT) | فیزیوتراپیست کودکان (Pediatric PT) | فیزیوتراپیست ثبت‌شده (RPT) | درمانگر</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Advantage Software Physical Therapy Advantage | نرم‌افزار بازی ویدئویی Biometrics | Cedaron Dexter Evaluation &amp; Impairment Rating | Clinicient Insight | نرم‌افزار ایجاد روتین ورزشی | Hands On Technology TheraWriter.PT | MEDITECH software | MediGraph | نرم‌افزار کدگذاری وضعیت پزشکی | نرم‌افزار کدگذاری رویه‌های پزشکی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word | نرم‌افزار نمودار بیمار | Prognosis Innovation Healthcare ChartAccess | نرم‌افزار ثبت سوابق | Rehab Documentation Company ReDoc Suite | SpectraSoft AppointmentsCS | نرم‌افزار eClinicalWorks EHR</t>
+          <t>Advantage Software Physical Therapy Advantage | نرم‌افزار بازی ویدئویی Biometrics | Cedaron Dexter Evaluation &amp; Impairment Rating | Clinicient Insight | نرم‌افزار ایجاد روتین ورزشی | Hands On Technology TheraWriter.PT | نرم‌افزار MEDITECH | MediGraph | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری رویه‌های پزشکی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word | نرم‌افزار نمودار بیمار | Prognosis Innovation Healthcare ChartAccess | نرم‌افزار ثبت سوابق | Rehab Documentation Company ReDoc Suite | SpectraSoft AppointmentsCS | نرم‌افزار eClinicalWorks EHR</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخنوری | گوش دادن فعال | درک مطلب | نوشتار | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>خدمات مشتری و شخصی | درمان و مشاوره | پزشکی و دندانپزشکی | روان‌شناسی | زبان انگلیسی | آموزش و پرورش | زیست‌شناسی | فیزیک | مدیریت و اداره | جامعه‌شناسی و مردم‌شناسی | اداری</t>
+          <t>خدمات مشتری و شخصی | درمان و مشاوره | پزشکی و دندان‌پزشکی | روان‌شناسی | زبان انگلیسی | آموزش و پرورش | زیست‌شناسی | فیزیک | مدیریت و اداره | جامعه‌شناسی و انسان‌شناسی | اداری</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | بیان نوشتاری | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | نظم‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | دید نزدیک | روانی ایده‌ها | ثبات دست و بازو | قدرت تنه | قدرت ایستا | مهارت انگشتان | توجه انتخابی | دید دور | مهارت دستی | انعطاف‌پذیری دسته‌بندی | اصالت</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | روانی ایده‌ها | ثبات دست و بازو | قدرت تنه | قدرت ایستا | مهارت انگشتان | توجه انتخابی | بینایی دور | مهارت دستی | انعطاف‌پذیری دسته‌بندی | اصالت</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>تماس با دیگران | نزدیکی فیزیکی | محیط داخلی، دارای کنترل محیطی | بحث‌های حضوری با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | تناوب تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | فشار زمانی | سلامت و ایمنی سایر کارکنان | نتایج کاری و عملکرد سایر کارکنان | ایمیل | صرف زمان برای ایستادن | پیامد خطا | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | اهمیت تکرار وظایف یکسان | نامه‌ها و یادداشت‌های کتبی | اهمیت دقیق یا صحیح بودن | در معرض بیماری یا عفونت</t>
+          <t>ارتباط با دیگران | نزدیکی فیزیکی | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | فراوانی تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی | سلامت و ایمنی سایر کارکنان | پیامدهای کاری و نتایج سایر کارکنان | ایمیل | صرف زمان برای ایستادن | پیامد خطا | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | اهمیت تکرار وظایف یکسان | نامه‌ها و یادداشت‌های کتبی | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Acute Care Nurses | Advanced Practice Psychiatric Nurses | Clinical Nurse Specialists | Emergency Medicine Physicians | Family Medicine Physicians | Nurse Practitioners | Occupational Therapists | Occupational Therapy Aides | Occupational Therapy Assistants | Orthopedic Surgeons, Except Pediatric | Pediatric Surgeons | Pediatricians, General | Physical Medicine and Rehabilitation Physicians | Physical Therapist Aides | Physical Therapist Assistants | Psychiatric Technicians | Radiation Therapists | Recreational Therapists | Registered Nurses | Respiratory Therapists</t>
+          <t>پرستاران مراقبت‌های ویژه | پرستاران پیشرفته روانپزشکی | متخصصان پرستاری بالینی | پزشکان طب اورژانس | پزشکان خانواده | پرستاران متخصص | کاردرمانگران | کمک‌یاران کاردرمانی | دستیاران کاردرمانی | جراحان ارتوپد، به‌جز کودکان | جراحان کودکان | متخصصان کودکان، عمومی | پزشکان طب فیزیکی و توانبخشی | کمک‌یاران فیزیوتراپی | دستیاران فیزیوتراپی | تکنسین‌های روانپزشکی | پرتودرمانگران | درمانگران تفریحی | پرستاران ثبت‌شده | درمانگران تنفسی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -835,12 +835,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Radiation Therapists (پرتودرمانگران)</t>
+          <t>پرتودرمانگران (Radiation Therapists)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Computed Tomography Simulation Therapist (CT Simulation Therapist) | Dosimetrist | Radiation Therapist (RT) | Radiation Therapy Technology (RTT) | Registered Radiation Therapist | Staff Radiation Therapist</t>
+          <t>درمانگر شبیه‌سازی سی‌تی‌اسکن (CT Simulation) | دوزیمتریست | پرتودرمانگر (RT) | تکنولوژیست پرتودرمانی (RTT) | پرتودرمانگر ثبت‌شده | پرتودرمانگر کادر درمان</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -850,27 +850,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخنوری | نظارت | نوشتار | یادگیری فعال</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | نظارت | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتری و شخصی | زبان انگلیسی | پزشکی و دندانپزشکی | فیزیک | ریاضیات | آموزش و پرورش | رایانه و الکترونیک | درمان و مشاوره | روان‌شناسی | زیست‌شناسی | اداری</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | پزشکی و دندان‌پزشکی | فیزیک | ریاضیات | آموزش و پرورش | رایانه و الکترونیک | درمان و مشاوره | روان‌شناسی | زیست‌شناسی | اداری</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شنیداری | بیان شفاهی | حساسیت به مسئله | درک نوشتاری | بیان نوشتاری | نظم‌دهی اطلاعات | استدلال قیاسی | وضوح گفتار | دید نزدیک | ثبات دست و بازو | تشخیص گفتار | استدلال استقرایی | دقت کنترل | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | دید دور | تجسم | انعطاف‌پذیری بستار | روانی ایده‌ها | هماهنگی چند اندامی | مهارت انگشتان | مهارت دستی</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | درک کتبی | بیان کتبی | ترتیب‌دهی اطلاعات | استدلال قیاسی | وضوح گفتار | بینایی نزدیک | ثبات دست و بازو | تشخیص گفتار | استدلال استقرایی | دقت کنترل | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | بینایی دور | تجسم | انعطاف‌پذیری بستار | روانی ایده‌ها | هماهنگی چند عضو | مهارت انگشتان | مهارت دستی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>تماس با دیگران | نزدیکی فیزیکی | اهمیت دقیق یا صحیح بودن | در معرض بیماری یا عفونت | بحث‌های حضوری با افراد و درون تیم‌ها | ایمیل | مکالمات تلفنی | اهمیت تکرار وظایف یکسان | محیط داخلی، دارای کنترل محیطی | پیامد خطا | فشار زمانی | صرف زمان برای استفاده از دست‌ها جهت کار با، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تناوب تصمیم‌گیری | آزادی در تصمیم‌گیری | صرف زمان برای انجام حرکات تکراری | صرف زمان برای راه رفتن یا دویدن | سطح رقابت | صرف زمان برای ایستادن | تعیین وظایف، اولویت‌ها و اهداف | سلامت و ایمنی سایر کارکنان | سرعت تعیین‌شده توسط سرعت تجهیزات | نتایج کاری و عملکرد سایر کارکنان | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری</t>
+          <t>ارتباط با دیگران | نزدیکی فیزیکی | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ایمیل | مکالمات تلفنی | اهمیت تکرار وظایف یکسان | محیط داخلی، دارای کنترل شرایط محیطی | پیامد خطا | فشار زمانی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | صرف زمان برای انجام حرکات تکراری | صرف زمان برای راه رفتن یا دویدن | سطح رقابت | صرف زمان برای ایستادن | تعیین وظایف، اولویت‌ها و اهداف | سلامت و ایمنی سایر کارکنان | سرعت تعیین‌شده توسط سرعت تجهیزات | پیامدهای کاری و نتایج سایر کارکنان | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Acute Care Nurses | Anesthesiologist Assistants | Cardiologists | Cardiovascular Technologists and Technicians | Diagnostic Medical Sonographers | Emergency Medicine Physicians | Magnetic Resonance Imaging Technologists | Medical Dosimetrists | Neurodiagnostic Technologists | Nuclear Medicine Technologists | Orthopedic Surgeons, Except Pediatric | Pediatric Surgeons | Physical Medicine and Rehabilitation Physicians | Physical Therapist Aides | Physical Therapist Assistants | Physical Therapists | Radiologic Technologists and Technicians | Radiologists | Respiratory Therapists | Surgical Assistants</t>
+          <t>پرستاران مراقبت‌های ویژه | دستیاران متخصص بیهوشی | متخصصان قلب | تکنولوژیست‌ها و تکنیسین‌های قلبی-عروقی | سونوگرافیست‌های پزشکی تشخیصی | پزشکان طب اورژانس | تکنولوژیست‌های تصویربرداری تشدید مغناطیسی | دوزیمتریست‌های پزشکی | تکنولوژیست‌های نورودیاگنوستیک | تکنولوژیست‌های پزشکی هسته‌ای | جراحان ارتوپد، به‌جز کودکان | جراحان کودکان | پزشکان طب فیزیکی و توانبخشی | کمک‌یاران فیزیوتراپی | دستیاران فیزیوتراپی | فیزیوتراپیست‌ها | تکنولوژیست‌ها و تکنسین‌های رادیولوژی | رادیولوژیست‌ها | درمانگران تنفسی | دستیاران جراحی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -892,42 +892,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Recreational Therapists (درمانگران تفریحی)</t>
+          <t>درمانگران تفریحی (Recreational Therapists)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Activities Coordinator | Certified Therapeutic Recreation Specialist (CTRS) | General Activities Therapist | Recreation Therapist | Recreational Therapist | Recreational Therapy Program Coordinator | Rehabilitation Therapist | Therapeutic Recreation Specialist | Therapeutic Specialist | Therapist</t>
+          <t>هماهنگ‌کننده فعالیت‌ها | کارشناس تفریحات درمانی دارای گواهی صلاحیت (CTRS) | درمانگر فعالیت‌های عمومی | تفریح‌درمانگر | تفریح‌درمانگر | هماهنگ‌کننده برنامه تفریح‌درمانی | درمانگر توانبخشی | کارشناس تفریحات درمانی | کارشناس درمان | درمانگر</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Avid Technology Sibelius | نرم‌افزار ایمیل | Hyperscore | MakeMusic Finale | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار رابط دیجیتال سازهای موسیقی MIDI | نرم‌افزار پرونده الکترونیک سلامت EMR بیمار | نرم‌افزار تشخیص گفتار | Steinberg Cubase Pro | نرم‌افزار مرورگر وب</t>
+          <t>Avid Technology Sibelius | نرم‌افزار ایمیل | Hyperscore | MakeMusic Finale | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار رابط دیجیتال سازهای موسیقی MIDI | نرم‌افزار پرونده الکترونیک سلامت بیمار EMR | نرم‌افزار تشخیص گفتار | Steinberg Cubase Pro | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>سخنوری | گوش دادن فعال | درک مطلب | نوشتار | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>روان‌شناسی | درمان و مشاوره | خدمات مشتری و شخصی | آموزش و پرورش | زبان انگلیسی | جامعه‌شناسی و مردم‌شناسی | مدیریت و اداره | پزشکی و دندانپزشکی | ایمنی و امنیت عمومی</t>
+          <t>روان‌شناسی | درمان و مشاوره | خدمات مشتری و شخصی | آموزش و پرورش | زبان انگلیسی | جامعه‌شناسی و انسان‌شناسی | مدیریت و اداره | پزشکی و دندان‌پزشکی | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شنیداری | بیان شفاهی | وضوح گفتار | درک نوشتاری | بیان نوشتاری | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | نظم‌دهی اطلاعات | اصالت | دید نزدیک | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | انعطاف‌پذیری بستار | دید دور | اشتراک زمانی | توجه انتخابی</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | ترتیب‌دهی اطلاعات | اصالت | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | انعطاف‌پذیری بستار | بینایی دور | تقسیم توجه | توجه انتخابی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>بحث‌های حضوری با افراد و درون تیم‌ها | تماس با دیگران | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل محیطی | نزدیکی فیزیکی | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | مکالمات تلفنی | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | در معرض بیماری یا عفونت | تعامل با مشتریان خارجی یا عموم مردم | سلامت و ایمنی سایر کارکنان | فشار زمانی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | سخنرانی عمومی</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | نزدیکی فیزیکی | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | مکالمات تلفنی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | تعامل با مشتریان خارجی یا عموم مردم | سلامت و ایمنی سایر کارکنان | فشار زمانی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | سخنرانی عمومی</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Advanced Practice Psychiatric Nurses | Art Therapists | Clinical Nurse Specialists | Clinical and Counseling Psychologists | Marriage and Family Therapists | Massage Therapists | Mental Health Counselors | Mental Health and Substance Abuse Social Workers | Music Therapists | Occupational Therapists | Occupational Therapy Aides | Occupational Therapy Assistants | Physical Medicine and Rehabilitation Physicians | Physical Therapist Aides | Physical Therapist Assistants | Physical Therapists | Psychiatric Aides | Psychiatric Technicians | Psychiatrists | Rehabilitation Counselors</t>
+          <t>پرستاران پیشرفته روانپزشکی | هنردرمانگران | متخصصان پرستاری بالینی | روان‌شناسان بالینی و مشاوره | درمانگران ازدواج و خانواده | ماساژدرمانگران | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | موسیقی‌درمانگران | کاردرمانگران | کمک‌یاران کاردرمانی | دستیاران کاردرمانی | پزشکان طب فیزیکی و توانبخشی | کمک‌یاران فیزیوتراپی | دستیاران فیزیوتراپی | فیزیوتراپیست‌ها | کمک‌یاران روان‌پزشکی | تکنسین‌های روانپزشکی | روان‌پزشکان | مشاوران توانبخشی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -949,42 +949,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Respiratory Therapists (درمانگران تنفسی)</t>
+          <t>درمانگران تنفسی (Respiratory Therapists)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cardiopulmonary Rehabilitation Respiratory Therapist | Certified Respiratory Therapist (CRT) | Registered Respiratory Therapist (RRT) | Respiratory Care Practitioner (RCP) | Respiratory Therapist (RT) | Staff Respiratory Therapist | Staff Therapist</t>
+          <t>تنفس‌درمانگر توان‌بخشی قلبی‌ریوی | تنفس‌درمانگر دارای گواهی صلاحیت (CRT) | تنفس‌درمانگر ثبت‌شده (RRT) | درمانگر مراقبت تنفسی (RCP) | تنفس‌درمانگر (RT) | تنفس‌درمانگر کادر درمان | درمانگر کادر درمان</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>نرم‌افزار پایگاه داده | نرم‌افزار پرونده الکترونیک سلامت EMR | HMS | MEDITECH software | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار eClinicalWorks EHR</t>
+          <t>نرم‌افزار پایگاه داده | نرم‌افزار پرونده الکترونیک سلامت EMR | HMS | نرم‌افزار MEDITECH | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار eClinicalWorks EHR</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | تفکر انتقادی | نظارت | سخنوری | درک مطلب | یادگیری فعال | راهبردهای یادگیری | نوشتار | علوم</t>
+          <t>گوش دادن فعال | تفکر انتقادی | نظارت | سخن گفتن | درک مطلب | یادگیری فعال | راهبردهای یادگیری | نگارش | علوم</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتری و شخصی | پزشکی و دندانپزشکی | زبان انگلیسی | آموزش و پرورش | روان‌شناسی | زیست‌شناسی | رایانه و الکترونیک | شیمی | ریاضیات</t>
+          <t>خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | زبان انگلیسی | آموزش و پرورش | روان‌شناسی | زیست‌شناسی | رایانه و الکترونیک | شیمی | ریاضیات</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بیان شفاهی | حساسیت به مسئله | استدلال استقرایی | درک شنیداری | استدلال قیاسی | نظم‌دهی اطلاعات | درک نوشتاری | دید نزدیک | بیان نوشتاری | وضوح گفتار | تشخیص گفتار | سرعت ادراکی | مهارت انگشتان | مهارت دستی | توجه انتخابی | دید دور | هماهنگی چند اندامی | دقت کنترل | ثبات دست و بازو | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی</t>
+          <t>بیان شفاهی | حساسیت به مسئله | استدلال استقرایی | درک شفاهی | استدلال قیاسی | ترتیب‌دهی اطلاعات | درک کتبی | بینایی نزدیک | بیان کتبی | وضوح گفتار | تشخیص گفتار | سرعت ادراکی | مهارت انگشتان | مهارت دستی | توجه انتخابی | بینایی دور | هماهنگی چند عضو | دقت کنترل | ثبات دست و بازو | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>مکالمات تلفنی | بحث‌های حضوری با افراد و درون تیم‌ها | در معرض بیماری یا عفونت | تماس با دیگران | محیط داخلی، دارای کنترل محیطی | نزدیکی فیزیکی | تناوب تصمیم‌گیری | اهمیت دقیق یا صحیح بودن | کار با یا مشارکت در یک گروه کاری یا تیم | پیامد خطا | تأثیر تصمیمات بر همکاران یا نتایج شرکت | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | تعامل با مشتریان خارجی یا عموم مردم | ایمیل | فشار زمانی | صرف زمان برای استفاده از دست‌ها جهت کار با، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای راه رفتن یا دویدن | صرف زمان برای ایستادن | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | در معرض آلاینده‌ها | اهمیت تکرار وظایف یکسان | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب</t>
+          <t>مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | نزدیکی فیزیکی | فراوانی تصمیم‌گیری | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | پیامد خطا | تأثیر تصمیمات بر همکاران یا نتایج شرکت | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | تعامل با مشتریان خارجی یا عموم مردم | ایمیل | فشار زمانی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای راه رفتن یا دویدن | صرف زمان برای ایستادن | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض آلاینده‌ها | اهمیت تکرار وظایف یکسان | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Acute Care Nurses | Anesthesiologist Assistants | Anesthesiologists | Cardiologists | Cardiovascular Technologists and Technicians | Clinical Nurse Specialists | Critical Care Nurses | Emergency Medicine Physicians | Nurse Anesthetists | Nurse Practitioners | Occupational Therapy Assistants | Orthopedic Surgeons, Except Pediatric | Paramedics | Pediatric Surgeons | Physical Medicine and Rehabilitation Physicians | Physical Therapist Aides | Physical Therapist Assistants | Physical Therapists | Radiation Therapists | Registered Nurses</t>
+          <t>پرستاران مراقبت‌های ویژه | دستیاران متخصص بیهوشی | متخصصان بیهوشی | متخصصان قلب | تکنولوژیست‌ها و تکنیسین‌های قلبی-عروقی | متخصصان پرستاری بالینی | پرستاران بخش مراقبت‌های ویژه | پزشکان طب اورژانس | پرستاران بیهوشی | پرستاران متخصص | دستیاران کاردرمانی | جراحان ارتوپد، به‌جز کودکان | پارامدیک‌ها | جراحان کودکان | پزشکان طب فیزیکی و توانبخشی | کمک‌یاران فیزیوتراپی | دستیاران فیزیوتراپی | فیزیوتراپیست‌ها | پرتودرمانگران | پرستاران ثبت‌شده</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Speech-Language Pathologists (آسیب‌شناسان گفتار و زبان)</t>
+          <t>آسیب‌شناسان گفتار و زبان (Speech-Language Pathologists)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bilingual Speech-Language Pathologist (Bilingual SLP) | Pediatric Speech-Language Pathologist (Pediatric SLP) | Speech Clinician | Speech Pathologist | Speech Therapist | Speech and Language Clinician | Speech and Language Specialist | Speech and Language Teacher | Speech and Language Therapist | Speech-Language Pathologist (SLP)</t>
+          <t>گفتاردرمانگر دوزبانه (SLP) | گفتاردرمانگر کودکان (Pediatric SLP) | درمانگر گفتار | آسیب‌شناس گفتار | گفتاردرمانگر | درمانگر گفتار و زبان | کارشناس گفتار و زبان | معلم گفتار و زبان | گفتار و زبان‌درمانگر | آسیب‌شناس گفتار و زبان (SLP)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1021,27 +1021,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | راهبردهای یادگیری | سخنوری | نوشتار | یادگیری فعال | نظارت</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | راهبردهای یادگیری | سخن گفتن | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | آموزش و پرورش | خدمات مشتری و شخصی | روان‌شناسی | درمان و مشاوره | اداری | جامعه‌شناسی و مردم‌شناسی | پزشکی و دندانپزشکی</t>
+          <t>زبان انگلیسی | آموزش و پرورش | خدمات مشتری و شخصی | روان‌شناسی | درمان و مشاوره | اداری | جامعه‌شناسی و انسان‌شناسی | پزشکی و دندان‌پزشکی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شنیداری | تشخیص گفتار | بیان نوشتاری | بیان شفاهی | درک نوشتاری | وضوح گفتار | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | نظم‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | دید نزدیک | حساسیت شنوایی | اصالت | انعطاف‌پذیری بستار | توجه شنیداری | سرعت ادراکی | سرعت بستار | توجه انتخابی</t>
+          <t>درک شفاهی | تشخیص گفتار | بیان کتبی | بیان شفاهی | درک کتبی | وضوح گفتار | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | بینایی نزدیک | حساسیت شنوایی | اصالت | انعطاف‌پذیری بستار | توجه شنیداری | سرعت ادراکی | سرعت بستار | توجه انتخابی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>بحث‌های حضوری با افراد و درون تیم‌ها | تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | نزدیکی فیزیکی | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | فشار زمانی | تناوب تصمیم‌گیری | محیط داخلی، دارای کنترل محیطی | ایمیل | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا صحیح بودن | صرف زمان برای نشستن | تعامل با مشتریان خارجی یا عموم مردم | مکالمات تلفنی | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | نزدیکی فیزیکی | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | فشار زمانی | فراوانی تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | ایمیل | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا درست بودن | صرف زمان برای نشستن | تعامل با مشتریان خارجی یا عموم مردم | مکالمات تلفنی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Advanced Practice Psychiatric Nurses | Audiologists | Clinical Neuropsychologists | Clinical Nurse Specialists | Clinical and Counseling Psychologists | Family Medicine Physicians | Low Vision Therapists, Orientation and Mobility Specialists, and Vision Rehabilitation Therapists | Marriage and Family Therapists | Mental Health Counselors | Mental Health and Substance Abuse Social Workers | Nurse Practitioners | Occupational Therapists | Occupational Therapy Aides | Occupational Therapy Assistants | Physical Therapist Assistants | Physical Therapists | Psychiatric Technicians | Psychiatrists | Recreational Therapists | Speech-Language Pathology Assistants</t>
+          <t>پرستاران پیشرفته روانپزشکی | شنوایی‌شناسان | عصب‌روان‌شناسان بالینی | متخصصان پرستاری بالینی | روان‌شناسان بالینی و مشاوره | پزشکان خانواده | درمانگران کم‌بینایی، متخصصان جهت‌یابی و تحرک، و درمانگران توانبخشی بینایی | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | پرستاران متخصص | کاردرمانگران | کمک‌یاران کاردرمانی | دستیاران کاردرمانی | دستیاران فیزیوتراپی | فیزیوتراپیست‌ها | تکنسین‌های روانپزشکی | روان‌پزشکان | درمانگران تفریحی | دستیاران آسیب‌شناسی گفتار-زبان</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0043_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0043_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | سخن گفتن | نگارش | شنیدن فعال | یادگیری فعال | نظارت | علوم پایه | راهبردهای یادگیری | ریاضیات</t>
+          <t>تفکر انتقادی | درک مطلب | سخن گفتن | نگارش | گوش دادن فعال | یادگیری فعال | نظارت | علوم | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | زبان انگلیسی | روان‌شناسی | درمان و مشاوره | خدمات مشتریان و خدمات فردی | آموزش و تدریس | جامعه‌شناسی و مردم‌شناسی | رایانه و الکترونیک | شیمی | ریاضیات | ایمنی و امنیت عمومی</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | زبان انگلیسی | روان‌شناسی | درمان و مشاوره | خدمات مشتری و شخصی | آموزش و پرورش | جامعه‌شناسی و انسان‌شناسی | رایانه و الکترونیک | شیمی | ریاضیات | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک کتبی | بیان شفاهی | بیان کتبی | مرتب‌سازی اطلاعات | تشخیص گفتار | وضوح گفتار | دید نزدیک | انعطاف‌پذیری در طبقه‌بندی | کشف ساختارها | ثبات دست و بازو | سرعت ادراک | استدلال ریاضی | تشخیص تمایز رنگ‌ها | دید دور | چابکی انگشتان | روانی کلام و ایده</t>
+          <t>درک شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک کتبی | بیان شفاهی | بیان کتبی | ترتیب‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | ثبات دست و بازو | سرعت ادراکی | استدلال ریاضی | تشخیص رنگ بصری | بینایی دور | مهارت انگشتان | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های حاد | پرستاران روان‌پزشکی با تخصص پیشرفته | دستیاران متخصص بیهوشی | متخصصان بیهوشی | متخصصان قلب و عروق | پرستاران متخصص بالینی | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | دستیاران پزشک و پیراپزشکان بالینی | متخصصان مغز و اعصاب | پرستاران بالینی پیشرفته (Nurse Practitioners) | پزشکان متخصص زنان و زایمان | جراحان ارتوپدی (غیر از کودکان) | کارشناسان فوریت‌های پزشکی (پارامدیک) | جراحان اطفال | پزشکان متخصص کودکان | متخصصان طب فیزیکی و توانبخشی | پرستاران رسمی | متخصصان کلیه و مجاری ادراری (اورولوژیست‌ها)</t>
+          <t>پرستاران مراقبت‌های حاد | پرستاران تخصصی روانپزشکی | دستیاران متخصص بیهوشی | متخصصان بیهوشی | متخصصان بیماری‌های قلب و عروق | پرستاران متخصص بالینی | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | کمک‌پزشکان و دستیاران مطب | متخصصان مغز و اعصاب | پرستاران بالینی پیشرفته | متخصصان زنان و زایمان | جراحان ارتوپدی، غیر از اطفال | امدادگران و تکنسین‌های اورژانس (پارامدیک‌ها) | جراحان اطفال | متخصصان عمومی کودکان | متخصصان طب فیزیکی و توانبخشی | پرستاران | متخصصان اورولوژی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | نظارت | سخن گفتن | تفکر انتقادی | یادگیری فعال | نگارش | علوم پایه</t>
+          <t>گوش دادن فعال | درک مطلب | نظارت | سخن گفتن | تفکر انتقادی | یادگیری فعال | نگارش | علوم</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>پزشکی و دندان‌پزشکی | زبان انگلیسی | شیمی | خدمات مشتریان و خدمات فردی | ریاضیات | زیست‌شناسی | آموزش و تدریس | رایانه و الکترونیک</t>
+          <t>پزشکی و دندان‌پزشکی | زبان انگلیسی | شیمی | خدمات مشتری و شخصی | ریاضیات | زیست‌شناسی | آموزش و پرورش | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مسئله | درک کتبی | استدلال قیاسی | استدلال استقرایی | دید نزدیک | بیان شفاهی | سرعت ادراک | توجه انتخابی | بیان کتبی | ثبات دست و بازو | مرتب‌سازی اطلاعات | تشخیص گفتار | وضوح گفتار | دقت کنترل ابزار | کشف ساختارها | چابکی دستی | چابکی انگشتان | انعطاف‌پذیری در طبقه‌بندی | سرعت درک الگوها | استدلال ریاضی | تشخیص تمایز رنگ‌ها | تقسیم توجه</t>
+          <t>درک شفاهی | حساسیت به مسئله | درک کتبی | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | بیان شفاهی | سرعت ادراکی | توجه انتخابی | بیان کتبی | ثبات دست و بازو | ترتیب‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | دقت کنترل | انعطاف‌پذیری بستار | مهارت دستی | مهارت انگشتان | انعطاف‌پذیری دسته‌بندی | سرعت بستار | استدلال ریاضی | تشخیص رنگ بصری | تقسیم توجه</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های حاد | متخصصان بیهوشی | متخصصان قلب و عروق | کارشناسان و تکنسین‌های قلب و عروق | پرستاران متخصص بالینی | پرستاران بخش مراقبت‌های ویژه (ICU) | تکنسین‌های فوریت‌های پزشکی | پزشکان طب اورژانس | هوشبَران و پرستاران بیهوشی | پرستاران بالینی پیشرفته (Nurse Practitioners) | جراحان ارتوپدی (غیر از کودکان) | کارشناسان فوریت‌های پزشکی (پارامدیک) | جراحان اطفال | متخصصان طب فیزیکی و توانبخشی | دستیاران پزشک | کارشناسان پرتو‌درمانی (رادیوتراپی) | پرستاران رسمی | کارشناسان مراقبت‌های تنفسی | دستیاران جراحی | کارشناسان اتاق عمل (تکنولوژیست‌های جراحی)</t>
+          <t>پرستاران مراقبت‌های حاد | متخصصان بیهوشی | متخصصان بیماری‌های قلب و عروق | کارشناسان و تکنسین‌های قلب و عروق | پرستاران متخصص بالینی | پرستاران مراقبت‌های ویژه | تکنسین‌های فوریت‌های پزشکی | پزشکان طب اورژانس | پرستاران بیهوشی | پرستاران بالینی پیشرفته | جراحان ارتوپدی، غیر از اطفال | امدادگران و تکنسین‌های اورژانس (پارامدیک‌ها) | جراحان اطفال | متخصصان طب فیزیکی و توانبخشی | دستیاران پزشک | پرتودرمانگران / کارشناسان رادیوتراپی | پرستاران | کارشناسان مراقبت‌های تنفسی / تنفس‌درمانگران | دستیاران جراحی | تکنسین‌های اتاق عمل</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>یادگیری فعال | تفکر انتقادی | سخن گفتن | شنیدن فعال | درک مطلب | نگارش | نظارت | علوم پایه | راهبردهای یادگیری</t>
+          <t>یادگیری فعال | تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | نظارت | علوم | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>پزشکی و دندان‌پزشکی | خدمات مشتریان و خدمات فردی | زبان انگلیسی | آموزش و تدریس | رایانه و الکترونیک | زیست‌شناسی | مدیریت و امور اداری | روان‌شناسی | شیمی | امور کارکنان و منابع انسانی | اقتصاد و حسابداری | درمان و مشاوره | امور اداری و سازمانی</t>
+          <t>پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | زبان انگلیسی | آموزش و پرورش | رایانه و الکترونیک | زیست‌شناسی | مدیریت و اداره | روان‌شناسی | شیمی | پرسنل و منابع انسانی | اقتصاد و حسابداری | درمان و مشاوره | اداری</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | استدلال استقرایی | درک کتبی | بیان کتبی | حساسیت به مسئله | درک شفاهی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | دید نزدیک | انعطاف‌پذیری در طبقه‌بندی | کشف ساختارها | مرتب‌سازی اطلاعات | روانی کلام و ایده | تجسم فضایی | سرعت درک الگوها | چابکی انگشتان | چابکی دستی | ثبات دست و بازو | توجه انتخابی | سرعت ادراک | توانایی به‌خاطرسپاری | خلاقیت و ابتکار</t>
+          <t>استدلال قیاسی | استدلال استقرایی | درک کتبی | بیان کتبی | حساسیت به مسئله | درک شفاهی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | روانی ایده‌ها | تجسم | سرعت بستار | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | توجه انتخابی | سرعت ادراکی | حفظ کردن | اصالت</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>متخصصان آلرژی و ایمنی‌شناسی بالینی | متخصصان بیهوشی | متخصصان قلب و عروق | متخصصان کایروپراکتیک (درمان دستی) | دندان‌پزشکان عمومی | متخصصان پوست، مو و زیبایی | پزشکان طب اورژانس | پزشکان متخصص بیماری‌های داخلی | دستیاران پزشک و پیراپزشکان بالینی | پزشکان طب طبیعی (ناتروپاتی) | متخصصان مغز و اعصاب | پزشکان متخصص زنان و زایمان | چشم‌پزشکان (غیر از کودکان) | اپتومتریست‌ها (بینایی‌سنج‌ها) | جراحان دهان، فک و صورت | متخصصان ارتودنسی | جراحان ارتوپدی (غیر از کودکان) | جراحان اطفال | متخصصان طب فیزیکی و توانبخشی | متخصصان کلیه و مجاری ادراری (اورولوژیست‌ها)</t>
+          <t>متخصصان آلرژی و ایمنی‌شناسی | متخصصان بیهوشی | متخصصان بیماری‌های قلب و عروق | کایروپراکتورها / متخصصان درمان دستی | دندان‌پزشکان عمومی | متخصصان پوست و مو | پزشکان طب اورژانس | پزشکان متخصص بیماری‌های داخلی | کمک‌پزشکان و دستیاران مطب | پزشکان طب طبیعی و نتوپاتی | متخصصان مغز و اعصاب | متخصصان زنان و زایمان | متخصصان چشم‌پزشکی، غیر از اطفال | بینایی‌سنج‌ها (اپتومتریست‌ها) | جراحان دهان، فک و صورت | متخصصان ارتودنسی | جراحان ارتوپدی، غیر از اطفال | جراحان اطفال | متخصصان طب فیزیکی و توانبخشی | متخصصان اورولوژی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>شنیدن فعال | نظارت | تفکر انتقادی | سخن گفتن | نگارش | درک مطلب | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | نظارت | تفکر انتقادی | سخن گفتن | نگارش | درک مطلب | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>درمان و مشاوره | روان‌شناسی | خدمات مشتریان و خدمات فردی | پزشکی و دندان‌پزشکی | زبان انگلیسی | آموزش و تدریس | زیست‌شناسی | جامعه‌شناسی و مردم‌شناسی</t>
+          <t>درمان و مشاوره | روان‌شناسی | خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | زبان انگلیسی | آموزش و پرورش | زیست‌شناسی | جامعه‌شناسی و انسان‌شناسی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | مرتب‌سازی اطلاعات | تشخیص گفتار | وضوح گفتار | روانی کلام و ایده | خلاقیت و ابتکار | دید نزدیک | انعطاف‌پذیری در طبقه‌بندی | توجه انتخابی | دید دور | چابکی انگشتان</t>
+          <t>بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | ترتیب‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | روانی ایده‌ها | اصالت | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | بینایی دور | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های حاد | پرستاران روان‌پزشکی با تخصص پیشرفته | پرستاران متخصص بالینی | پزشکان عمومی و خانواده | کارشناسان توانبخشی و جهت‌یابی نابینایان و کم‌بینایان | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و سوءمصرف مواد | پرستاران بالینی پیشرفته (Nurse Practitioners) | کمک‌کاردرمانگران | دستیاران کاردرمانی | متخصصان طب فیزیکی و توانبخشی | کمک‌فیزیوتراپ‌ها | دستیاران فیزیوتراپی | فیزیوتراپیست‌ها | تکنسین‌های بهداشت روان و روان‌پزشکی | روان‌پزشکان | کارشناسان تفریح‌درمانی | پرستاران رسمی | مشاوران توانبخشی | کارشناسان مراقبت‌های تنفسی</t>
+          <t>پرستاران مراقبت‌های حاد | پرستاران تخصصی روانپزشکی | پرستاران متخصص بالینی | پزشکان عمومی و خانواده | متخصصان جهت‌یابی، حرکت و توانبخشی نابینایان و کم‌بینایان | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | پرستاران بالینی پیشرفته | کمک‌یاران کاردرمانی | کاردان‌های کاردرمانی | متخصصان طب فیزیکی و توانبخشی | کمک‌یاران فیزیوتراپی | کاردان‌های فیزیوتراپی | فیزیوتراپیست‌ها | تکنسین‌های روان‌پزشکی و بهداشت روان | روان‌پزشکان | کارشناسان تفریح‌درمانی | پرستاران | مشاوران توانبخشی | کارشناسان مراقبت‌های تنفسی / تنفس‌درمانگران</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>راهبردهای یادگیری | سخن گفتن | شنیدن فعال | درک مطلب | نگارش | یادگیری فعال | نظارت | تفکر انتقادی</t>
+          <t>راهبردهای یادگیری | سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | یادگیری فعال | نظارت | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | آموزش و تدریس | روان‌شناسی | حمل‌ونقل و ترابری | خدمات مشتریان و خدمات فردی | درمان و مشاوره | ایمنی و امنیت عمومی | جامعه‌شناسی و مردم‌شناسی</t>
+          <t>زبان انگلیسی | آموزش و پرورش | روان‌شناسی | حمل و نقل | خدمات مشتری و شخصی | درمان و مشاوره | ایمنی و امنیت عمومی | جامعه‌شناسی و انسان‌شناسی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | حساسیت به مسئله | بیان کتبی | وضوح گفتار | تشخیص گفتار | استدلال قیاسی | انعطاف‌پذیری در طبقه‌بندی | مرتب‌سازی اطلاعات | استدلال استقرایی | روانی کلام و ایده | خلاقیت و ابتکار | دید دور | دید نزدیک | توجه انتخابی</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | حساسیت به مسئله | بیان کتبی | وضوح گفتار | تشخیص گفتار | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال استقرایی | روانی ایده‌ها | اصالت | بینایی دور | بینایی نزدیک | توجه انتخابی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مربیان تربیت بدنی تطبیقی و استثنایی | مشاوران و درمانگران ازدواج و خانواده | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و سوءمصرف مواد | کاردرمانگران | کمک‌کاردرمانگران | دستیاران کاردرمانی | متخصصان طب فیزیکی و توانبخشی | کمک‌فیزیوتراپ‌ها | دستیاران فیزیوتراپی | فیزیوتراپیست‌ها | بهیاران و کمک‌یاران روان‌پزشکی | تکنسین‌های بهداشت روان و روان‌پزشکی | کارشناسان تفریح‌درمانی | مشاوران توانبخشی | آموزگاران آموزش استثنایی دوره ابتدایی | مربیان پیش‌دبستانی آموزش استثنایی | دبیران آموزش استثنایی دوره متوسطه | آسیب‌شناسان گفتار و زبان (گفتاردرمانگران) | دستیاران گفتاردرمانی</t>
+          <t>متخصصان تربیت بدنی انطباقی | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | کاردرمانگران | کمک‌یاران کاردرمانی | کاردان‌های کاردرمانی | متخصصان طب فیزیکی و توانبخشی | کمک‌یاران فیزیوتراپی | کاردان‌های فیزیوتراپی | فیزیوتراپیست‌ها | کمک‌یاران بخش روان‌پزشکی | تکنسین‌های روان‌پزشکی و بهداشت روان | کارشناسان تفریح‌درمانی | مشاوران توانبخشی | معلمان آموزش استثنایی دوره آمادگی و نوآموزان | معلمان آموزش استثنایی دوره پیش‌دبستانی | دبیران آموزش استثنایی دوره دوم متوسطه | آسیب‌شناسان گفتار و زبان / گفتاردرمانگران | دستیاران آسیب‌شناسی گفتار و زبان (گفتاردرمانی)</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال | درک مطلب | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | درمان و مشاوره | پزشکی و دندان‌پزشکی | روان‌شناسی | زبان انگلیسی | آموزش و تدریس | زیست‌شناسی | فیزیک | مدیریت و امور اداری | جامعه‌شناسی و مردم‌شناسی | امور اداری و سازمانی</t>
+          <t>خدمات مشتری و شخصی | درمان و مشاوره | پزشکی و دندان‌پزشکی | روان‌شناسی | زبان انگلیسی | آموزش و پرورش | زیست‌شناسی | فیزیک | مدیریت و اداره | جامعه‌شناسی و انسان‌شناسی | اداری</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | تشخیص گفتار | وضوح گفتار | دید نزدیک | روانی کلام و ایده | ثبات دست و بازو | قدرت تنه | قدرت ایستا | چابکی انگشتان | توجه انتخابی | دید دور | چابکی دستی | انعطاف‌پذیری در طبقه‌بندی | خلاقیت و ابتکار</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | روانی ایده‌ها | ثبات دست و بازو | قدرت تنه | قدرت ایستا | مهارت انگشتان | توجه انتخابی | بینایی دور | مهارت دستی | انعطاف‌پذیری دسته‌بندی | اصالت</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های حاد | پرستاران روان‌پزشکی با تخصص پیشرفته | پرستاران متخصص بالینی | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پرستاران بالینی پیشرفته (Nurse Practitioners) | کاردرمانگران | کمک‌کاردرمانگران | دستیاران کاردرمانی | جراحان ارتوپدی (غیر از کودکان) | جراحان اطفال | پزشکان متخصص کودکان | متخصصان طب فیزیکی و توانبخشی | کمک‌فیزیوتراپ‌ها | دستیاران فیزیوتراپی | تکنسین‌های بهداشت روان و روان‌پزشکی | کارشناسان پرتو‌درمانی (رادیوتراپی) | کارشناسان تفریح‌درمانی | پرستاران رسمی | کارشناسان مراقبت‌های تنفسی</t>
+          <t>پرستاران مراقبت‌های حاد | پرستاران تخصصی روانپزشکی | پرستاران متخصص بالینی | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پرستاران بالینی پیشرفته | کاردرمانگران | کمک‌یاران کاردرمانی | کاردان‌های کاردرمانی | جراحان ارتوپدی، غیر از اطفال | جراحان اطفال | متخصصان عمومی کودکان | متخصصان طب فیزیکی و توانبخشی | کمک‌یاران فیزیوتراپی | کاردان‌های فیزیوتراپی | تکنسین‌های روان‌پزشکی و بهداشت روان | پرتودرمانگران / کارشناسان رادیوتراپی | کارشناسان تفریح‌درمانی | پرستاران | کارشناسان مراقبت‌های تنفسی / تنفس‌درمانگران</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | سخن گفتن | نظارت | نگارش | یادگیری فعال</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | نظارت | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | پزشکی و دندان‌پزشکی | فیزیک | ریاضیات | آموزش و تدریس | رایانه و الکترونیک | درمان و مشاوره | روان‌شناسی | زیست‌شناسی | امور اداری و سازمانی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | پزشکی و دندان‌پزشکی | فیزیک | ریاضیات | آموزش و پرورش | رایانه و الکترونیک | درمان و مشاوره | روان‌شناسی | زیست‌شناسی | اداری</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | درک کتبی | بیان کتبی | مرتب‌سازی اطلاعات | استدلال قیاسی | وضوح گفتار | دید نزدیک | ثبات دست و بازو | تشخیص گفتار | استدلال استقرایی | دقت کنترل ابزار | توجه انتخابی | انعطاف‌پذیری در طبقه‌بندی | دید دور | تجسم فضایی | کشف ساختارها | روانی کلام و ایده | هماهنگی چند اندام | چابکی انگشتان | چابکی دستی</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | درک کتبی | بیان کتبی | ترتیب‌دهی اطلاعات | استدلال قیاسی | وضوح گفتار | بینایی نزدیک | ثبات دست و بازو | تشخیص گفتار | استدلال استقرایی | دقت کنترل | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | بینایی دور | تجسم | انعطاف‌پذیری بستار | روانی ایده‌ها | هماهنگی چند عضو | مهارت انگشتان | مهارت دستی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های حاد | دستیاران متخصص بیهوشی | متخصصان قلب و عروق | کارشناسان و تکنسین‌های قلب و عروق | سونوگرافیست‌ها و کارشناسان سونوگرافی تشخیصی | پزشکان طب اورژانس | کارشناسان تصویربرداری تشدید مغناطیسی (MRI) | دوزیمتریست‌های پرتودرمانی | تکنسین‌های تشخیصی مغز و اعصاب | کارشناسان پزشکی هسته‌ای | جراحان ارتوپدی (غیر از کودکان) | جراحان اطفال | متخصصان طب فیزیکی و توانبخشی | کمک‌فیزیوتراپ‌ها | دستیاران فیزیوتراپی | فیزیوتراپیست‌ها | کارشناسان و تکنسین‌های رادیولوژی و پرتو‌نگاری | پزشکان رادیولوژیست | کارشناسان مراقبت‌های تنفسی | دستیاران جراحی</t>
+          <t>پرستاران مراقبت‌های حاد | دستیاران متخصص بیهوشی | متخصصان بیماری‌های قلب و عروق | کارشناسان و تکنسین‌های قلب و عروق | سونوگرافیست‌های تشخیصی / کارشناسان سونوگرافی | پزشکان طب اورژانس | کارشناسان تصویربرداری تشدید مغناطیسی (MRI) | دزیمتریست‌های پزشکی | تکنسین‌های الکترونورودیاگنوستیک | کارشناسان و تکنسین‌های پزشکی هسته‌ای | جراحان ارتوپدی، غیر از اطفال | جراحان اطفال | متخصصان طب فیزیکی و توانبخشی | کمک‌یاران فیزیوتراپی | کاردان‌های فیزیوتراپی | فیزیوتراپیست‌ها | کارشناسان و تکنسین‌های رادیولوژی و پرتونگاری | متخصصان رادیولوژی | کارشناسان مراقبت‌های تنفسی / تنفس‌درمانگران | دستیاران جراحی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>روان‌شناسی | درمان و مشاوره | خدمات مشتریان و خدمات فردی | آموزش و تدریس | زبان انگلیسی | جامعه‌شناسی و مردم‌شناسی | مدیریت و امور اداری | پزشکی و دندان‌پزشکی | ایمنی و امنیت عمومی</t>
+          <t>روان‌شناسی | درمان و مشاوره | خدمات مشتری و شخصی | آموزش و پرورش | زبان انگلیسی | جامعه‌شناسی و انسان‌شناسی | مدیریت و اداره | پزشکی و دندان‌پزشکی | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | مرتب‌سازی اطلاعات | خلاقیت و ابتکار | دید نزدیک | انعطاف‌پذیری در طبقه‌بندی | روانی کلام و ایده | کشف ساختارها | دید دور | تقسیم توجه | توجه انتخابی</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | ترتیب‌دهی اطلاعات | اصالت | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | انعطاف‌پذیری بستار | بینایی دور | تقسیم توجه | توجه انتخابی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>پرستاران روان‌پزشکی با تخصص پیشرفته | هنردرمانگران | پرستاران متخصص بالینی | روان‌شناسان بالینی و مشاوره | مشاوران و درمانگران ازدواج و خانواده | ماساژدرمانگران | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و سوءمصرف مواد | موسیقی‌درمانگران | کاردرمانگران | کمک‌کاردرمانگران | دستیاران کاردرمانی | متخصصان طب فیزیکی و توانبخشی | کمک‌فیزیوتراپ‌ها | دستیاران فیزیوتراپی | فیزیوتراپیست‌ها | بهیاران و کمک‌یاران روان‌پزشکی | تکنسین‌های بهداشت روان و روان‌پزشکی | روان‌پزشکان | مشاوران توانبخشی</t>
+          <t>پرستاران تخصصی روانپزشکی | هنر‌درمانگران | پرستاران متخصص بالینی | روان‌شناسان بالینی و مشاوران سلامت روان | درمانگران ازدواج و خانواده | ماساژدرمانگران | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | موسیقی‌درمانگران | کاردرمانگران | کمک‌یاران کاردرمانی | کاردان‌های کاردرمانی | متخصصان طب فیزیکی و توانبخشی | کمک‌یاران فیزیوتراپی | کاردان‌های فیزیوتراپی | فیزیوتراپیست‌ها | کمک‌یاران بخش روان‌پزشکی | تکنسین‌های روان‌پزشکی و بهداشت روان | روان‌پزشکان | مشاوران توانبخشی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | نظارت | سخن گفتن | درک مطلب | یادگیری فعال | راهبردهای یادگیری | نگارش | علوم پایه</t>
+          <t>گوش دادن فعال | تفکر انتقادی | نظارت | سخن گفتن | درک مطلب | یادگیری فعال | راهبردهای یادگیری | نگارش | علوم</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | پزشکی و دندان‌پزشکی | زبان انگلیسی | آموزش و تدریس | روان‌شناسی | زیست‌شناسی | رایانه و الکترونیک | شیمی | ریاضیات</t>
+          <t>خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | زبان انگلیسی | آموزش و پرورش | روان‌شناسی | زیست‌شناسی | رایانه و الکترونیک | شیمی | ریاضیات</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بیان شفاهی | حساسیت به مسئله | استدلال استقرایی | درک شفاهی | استدلال قیاسی | مرتب‌سازی اطلاعات | درک کتبی | دید نزدیک | بیان کتبی | وضوح گفتار | تشخیص گفتار | سرعت ادراک | چابکی انگشتان | چابکی دستی | توجه انتخابی | دید دور | هماهنگی چند اندام | دقت کنترل ابزار | ثبات دست و بازو | کشف ساختارها | انعطاف‌پذیری در طبقه‌بندی</t>
+          <t>بیان شفاهی | حساسیت به مسئله | استدلال استقرایی | درک شفاهی | استدلال قیاسی | ترتیب‌دهی اطلاعات | درک کتبی | بینایی نزدیک | بیان کتبی | وضوح گفتار | تشخیص گفتار | سرعت ادراکی | مهارت انگشتان | مهارت دستی | توجه انتخابی | بینایی دور | هماهنگی چند عضو | دقت کنترل | ثبات دست و بازو | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های حاد | دستیاران متخصص بیهوشی | متخصصان بیهوشی | متخصصان قلب و عروق | کارشناسان و تکنسین‌های قلب و عروق | پرستاران متخصص بالینی | پرستاران بخش مراقبت‌های ویژه (ICU) | پزشکان طب اورژانس | هوشبَران و پرستاران بیهوشی | پرستاران بالینی پیشرفته (Nurse Practitioners) | دستیاران کاردرمانی | جراحان ارتوپدی (غیر از کودکان) | کارشناسان فوریت‌های پزشکی (پارامدیک) | جراحان اطفال | متخصصان طب فیزیکی و توانبخشی | کمک‌فیزیوتراپ‌ها | دستیاران فیزیوتراپی | فیزیوتراپیست‌ها | کارشناسان پرتو‌درمانی (رادیوتراپی) | پرستاران رسمی</t>
+          <t>پرستاران مراقبت‌های حاد | دستیاران متخصص بیهوشی | متخصصان بیهوشی | متخصصان بیماری‌های قلب و عروق | کارشناسان و تکنسین‌های قلب و عروق | پرستاران متخصص بالینی | پرستاران مراقبت‌های ویژه | پزشکان طب اورژانس | پرستاران بیهوشی | پرستاران بالینی پیشرفته | کاردان‌های کاردرمانی | جراحان ارتوپدی، غیر از اطفال | امدادگران و تکنسین‌های اورژانس (پارامدیک‌ها) | جراحان اطفال | متخصصان طب فیزیکی و توانبخشی | کمک‌یاران فیزیوتراپی | کاردان‌های فیزیوتراپی | فیزیوتراپیست‌ها | پرتودرمانگران / کارشناسان رادیوتراپی | پرستاران</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | راهبردهای یادگیری | سخن گفتن | نگارش | یادگیری فعال | نظارت</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | راهبردهای یادگیری | سخن گفتن | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | آموزش و تدریس | خدمات مشتریان و خدمات فردی | روان‌شناسی | درمان و مشاوره | امور اداری و سازمانی | جامعه‌شناسی و مردم‌شناسی | پزشکی و دندان‌پزشکی</t>
+          <t>زبان انگلیسی | آموزش و پرورش | خدمات مشتری و شخصی | روان‌شناسی | درمان و مشاوره | اداری | جامعه‌شناسی و انسان‌شناسی | پزشکی و دندان‌پزشکی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | تشخیص گفتار | بیان کتبی | بیان شفاهی | درک کتبی | وضوح گفتار | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | انعطاف‌پذیری در طبقه‌بندی | روانی کلام و ایده | دید نزدیک | حساسیت شنوایی | خلاقیت و ابتکار | کشف ساختارها | توجه شنوایی | سرعت ادراک | سرعت درک الگوها | توجه انتخابی</t>
+          <t>درک شفاهی | تشخیص گفتار | بیان کتبی | بیان شفاهی | درک کتبی | وضوح گفتار | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | بینایی نزدیک | حساسیت شنوایی | اصالت | انعطاف‌پذیری بستار | توجه شنیداری | سرعت ادراکی | سرعت بستار | توجه انتخابی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>پرستاران روان‌پزشکی با تخصص پیشرفته | شنوایی‌شناسان (ادیولوژیست‌ها) | نوروسایکولوژیست‌های بالینی | پرستاران متخصص بالینی | روان‌شناسان بالینی و مشاوره | پزشکان عمومی و خانواده | کارشناسان توانبخشی و جهت‌یابی نابینایان و کم‌بینایان | مشاوران و درمانگران ازدواج و خانواده | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و سوءمصرف مواد | پرستاران بالینی پیشرفته (Nurse Practitioners) | کاردرمانگران | کمک‌کاردرمانگران | دستیاران کاردرمانی | دستیاران فیزیوتراپی | فیزیوتراپیست‌ها | تکنسین‌های بهداشت روان و روان‌پزشکی | روان‌پزشکان | کارشناسان تفریح‌درمانی | دستیاران گفتاردرمانی</t>
+          <t>پرستاران تخصصی روانپزشکی | شنوایی‌شناسان | متخصصان عصب‌روان‌شناسی بالینی | پرستاران متخصص بالینی | روان‌شناسان بالینی و مشاوران سلامت روان | پزشکان عمومی و خانواده | متخصصان جهت‌یابی، حرکت و توانبخشی نابینایان و کم‌بینایان | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | پرستاران بالینی پیشرفته | کاردرمانگران | کمک‌یاران کاردرمانی | کاردان‌های کاردرمانی | کاردان‌های فیزیوتراپی | فیزیوتراپیست‌ها | تکنسین‌های روان‌پزشکی و بهداشت روان | روان‌پزشکان | کارشناسان تفریح‌درمانی | دستیاران آسیب‌شناسی گفتار و زبان (گفتاردرمانی)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
